--- a/docs/templates/jarvis_data_catalogue_template.xlsx
+++ b/docs/templates/jarvis_data_catalogue_template.xlsx
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>8</v>
